--- a/Composer/Composer_Test_Cases.xlsx
+++ b/Composer/Composer_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,47 +594,14 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>COMP_003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send Button</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty message not sent</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Leave input empty.
-2. Click send.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Message should not be sent.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
@@ -642,30 +609,38 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>COMP_004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
+          <t>COMP_003</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send Button</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, network disconnected</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify send fails without network</t>
+          <t>Verify empty message not sent</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Send message.</t>
+          <t>1. Leave input empty.
+2. Click send.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Error should display with retry option.</t>
+          <t>Message should not be sent.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -680,37 +655,30 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>COMP_005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attach Button</t>
-        </is>
-      </c>
+          <t>COMP_004</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify attach menu opens</t>
+          <t>Verify send fails without network</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Click attach (+) button.</t>
+          <t>1. Disconnect network.
+2. Send message.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Attachment options should display (Image, Video, Document).</t>
+          <t>Error should display with retry option.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -723,147 +691,122 @@
       <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>COMP_006</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>COMP_005</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attach Button</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify attach menu opens</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Click attach (+) button.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Attachment options should display (Image, Video, Document).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>COMP_006</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify sending image attachment</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Click attach.
 2. Select image.
 3. Send.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Image should upload and display in chat.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>COMP_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify sending document attachment</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Click attach.
 2. Select document.
 3. Send.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Document should upload with file icon and name.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>COMP_008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attach Button</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify file size limit exceeded</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Select file exceeding size limit.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>COMP_009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment upload failure</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Send attachment.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Error should display with retry option.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -876,204 +819,150 @@
       <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>COMP_008</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attach Button</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify file size limit exceeded</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Select file exceeding size limit.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>COMP_009</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment upload failure</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Send attachment.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Error should display with retry option.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>COMP_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Verify Recording Button</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify voice recording and send</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Press and hold mic button.
 2. Record.
 3. Release to send.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Voice message should be sent with play button.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>COMP_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify cancel recording</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Start recording.
-2. Slide to cancel.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Recording should be cancelled.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>COMP_012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>User has received voice message</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify playing voice message</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Click play on received voice message.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Voice message should play with progress.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>COMP_013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Verify Recording Button</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, mic permission denied</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify recording without permission</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Deny mic permission.
-2. Try to record.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Permission request or error should display.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>COMP_014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Emoji Button</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify emoji picker opens and selection</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Click emoji button.
-2. Select emoji.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Emoji should be added to input field.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1088,7 +977,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COMP_015</t>
+          <t>COMP_011</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1096,23 +985,23 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with emoji</t>
+          <t>Verify cancel recording</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Add emoji to message.
-2. Send.</t>
+          <t>1. Start recording.
+2. Slide to cancel.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Message with emoji should display correctly.</t>
+          <t>Recording should be cancelled.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
       <c r="I16" s="2" t="n"/>
@@ -1122,37 +1011,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>COMP_016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Verify Sticker Button</t>
-        </is>
-      </c>
+          <t>COMP_012</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User has received voice message</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker picker opens</t>
+          <t>Verify playing voice message</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Click sticker button.</t>
+          <t>1. Click play on received voice message.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Sticker picker should open with sticker packs.</t>
+          <t>Voice message should play with progress.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1165,35 +1046,14 @@
       <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>COMP_017</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending sticker</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1. Open sticker picker.
-2. Click sticker.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Sticker should be sent and display in chat.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
@@ -1201,39 +1061,38 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COMP_018</t>
+          <t>COMP_013</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Verify @all mention</t>
+          <t>Verify Recording Button</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in, mic permission denied</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify @all mention in group</t>
+          <t>Verify recording without permission</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@all".
-2. Select from suggestions.
-3. Send.</t>
+          <t>1. Deny mic permission.
+2. Try to record.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; all members notified.</t>
+          <t>Permission request or error should display.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1246,47 +1105,14 @@
       <c r="K19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>COMP_019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all mention</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all not available in direct chat</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1. Open direct chat.
-2. Type "@all".</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>@all suggestion should not appear.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
@@ -1294,7 +1120,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>COMP_020</t>
+          <t>COMP_014</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1304,27 +1130,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Verify @ mention</t>
+          <t>Verify Emoji Button</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify @ shows member suggestions</t>
+          <t>Verify emoji picker opens and selection</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@" in group chat.</t>
+          <t>1. Click emoji button.
+2. Select emoji.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Member list with avatars should appear.</t>
+          <t>Emoji should be added to input field.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1339,7 +1166,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COMP_021</t>
+          <t>COMP_015</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1347,17 +1174,18 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify filtering members by name</t>
+          <t>Verify sending message with emoji</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@Geo".</t>
+          <t>1. Add emoji to message.
+2. Send.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Only matching members should appear.</t>
+          <t>Message with emoji should display correctly.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1372,26 +1200,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COMP_022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
+          <t>COMP_016</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Verify Sticker Button</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify sending @ mention message</t>
+          <t>Verify sticker picker opens</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Select member.
-2. Send message.</t>
+          <t>1. Click sticker button.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Mentioned user should receive notification.</t>
+          <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1406,42 +1245,31 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COMP_023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
+          <t>COMP_017</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify @ with no matching members</t>
+          <t>Verify sending sticker</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@xyz123".</t>
+          <t>1. Open sticker picker.
+2. Click sticker.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>No suggestions should appear.</t>
+          <t>Sticker should be sent and display in chat.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -1451,7 +1279,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COMP_024</t>
+          <t>COMP_018</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1461,27 +1289,29 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify Composer in One-on-One chat</t>
+          <t>Verify @all mention</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and one-on-one chat is open</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify all features work in direct chat</t>
+          <t>Verify @all mention in group</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Test send, attach, record, emoji, sticker.</t>
+          <t>1. Type "@all".
+2. Select from suggestions.
+3. Send.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>All features should work except @all.</t>
+          <t>Message should be sent; all members notified.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1494,46 +1324,14 @@
       <c r="K25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>COMP_025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Verify Composer in Group chat</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Verify all features work in group chat</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1. Test all features including @mentions.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>All features should work including @all and @.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
@@ -1541,48 +1339,380 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COMP_026</t>
+          <t>COMP_019</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Verify UI responsiveness</t>
+          <t>Verify @all mention</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify composer on desktop and mobile</t>
+          <t>Verify @all not available in direct chat</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Test on desktop.
-2. Test on mobile.</t>
+          <t>1. Open direct chat.
+2. Type "@all".</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Composer should be functional on both platforms.</t>
+          <t>@all suggestion should not appear.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>COMP_020</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ shows member suggestions</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@" in group chat.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Member list with avatars should appear.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>COMP_021</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Verify filtering members by name</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@Geo".</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Only matching members should appear.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>COMP_022</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending @ mention message</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Select member.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Mentioned user should receive notification.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>COMP_023</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ with no matching members</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@xyz123".</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No suggestions should appear.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>COMP_024</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Verify Composer in One-on-One chat</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verify all features work in direct chat</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Test send, attach, record, emoji, sticker.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>All features should work except @all.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>COMP_025</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Verify Composer in Group chat</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verify all features work in group chat</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Test all features including @mentions.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>All features should work including @all and @.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>COMP_026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify composer on desktop and mobile</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Test on desktop.
+2. Test on mobile.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Composer should be functional on both platforms.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2229,7 +2359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2481,47 +2611,60 @@
       <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>COMP_042</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Composer</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify composer when keyboard is dismissed mid-typing</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Start typing.
 2. Dismiss keyboard (mobile).
 3. Reopen keyboard.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Typed text should persist. No data loss.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2535,7 +2678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2652,38 +2795,14 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>COMP_044</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message at max character limit + 1</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to type one character beyond the max limit.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Input should be blocked or warning should display.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
@@ -2691,30 +2810,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>COMP_045</t>
+          <t>COMP_044</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment at exactly max file size</t>
+          <t>Verify sending message at max character limit + 1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Attach a file at exactly the maximum allowed size.
-2. Send.</t>
+          <t>1. Try to type one character beyond the max limit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>File should upload and send successfully.</t>
+          <t>Input should be blocked or warning should display.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2727,41 +2845,105 @@
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>COMP_046</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment at max file size + 1 byte</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Attach a file 1 byte over the maximum size.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display. File should not upload.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>COMP_045</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment at exactly max file size</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Attach a file at exactly the maximum allowed size.
+2. Send.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>File should upload and send successfully.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>COMP_046</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment at max file size + 1 byte</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Attach a file 1 byte over the maximum size.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display. File should not upload.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Composer/Composer_Test_Cases.xlsx
+++ b/Composer/Composer_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,14 +594,46 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>COMP_005</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attach Button</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify attach menu opens</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Click attach (+) button.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Attachment options should display (Image, Video, Document).</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
@@ -609,38 +641,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>COMP_003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send Button</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>COMP_006</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Verify empty message not sent</t>
+          <t>Verify sending image attachment</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Leave input empty.
-2. Click send.</t>
+          <t>1. Click attach.
+2. Select image.
+3. Send.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Message should not be sent.</t>
+          <t>Image should upload and display in chat.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -655,30 +676,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>COMP_004</t>
+          <t>COMP_007</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify send fails without network</t>
+          <t>Verify sending document attachment</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Send message.</t>
+          <t>1. Click attach.
+2. Select document.
+3. Send.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Error should display with retry option.</t>
+          <t>Document should upload with file icon and name.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -691,14 +709,48 @@
       <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>COMP_010</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Verify Recording Button</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify voice recording and send</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Press and hold mic button.
+2. Record.
+3. Release to send.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Voice message should be sent with play button.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
@@ -706,42 +758,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>COMP_005</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attach Button</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>COMP_011</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify attach menu opens</t>
+          <t>Verify cancel recording</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Click attach (+) button.</t>
+          <t>1. Start recording.
+2. Slide to cancel.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Attachment options should display (Image, Video, Document).</t>
+          <t>Recording should be cancelled.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
       <c r="I8" s="2" t="n"/>
@@ -751,27 +792,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>COMP_006</t>
+          <t>COMP_012</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>User has received voice message</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify sending image attachment</t>
+          <t>Verify playing voice message</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Click attach.
-2. Select image.
-3. Send.</t>
+          <t>1. Click play on received voice message.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Image should upload and display in chat.</t>
+          <t>Voice message should play with progress.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -786,27 +829,38 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>COMP_007</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+          <t>COMP_014</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Emoji Button</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify sending document attachment</t>
+          <t>Verify emoji picker opens and selection</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Click attach.
-2. Select document.
-3. Send.</t>
+          <t>1. Click emoji button.
+2. Select emoji.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Document should upload with file icon and name.</t>
+          <t>Emoji should be added to input field.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -819,14 +873,35 @@
       <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>COMP_015</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message with emoji</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Add emoji to message.
+2. Send.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Message with emoji should display correctly.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
@@ -834,17 +909,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>COMP_008</t>
+          <t>COMP_016</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Verify Attach Button</t>
+          <t>Verify Sticker Button</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -854,22 +929,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify file size limit exceeded</t>
+          <t>Verify sticker picker opens</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Select file exceeding size limit.</t>
+          <t>1. Click sticker button.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Error message should display.</t>
+          <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
       <c r="I12" s="2" t="n"/>
@@ -879,30 +954,26 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>COMP_009</t>
+          <t>COMP_017</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment upload failure</t>
+          <t>Verify sending sticker</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Send attachment.</t>
+          <t>1. Open sticker picker.
+2. Click sticker.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Error should display with retry option.</t>
+          <t>Sticker should be sent and display in chat.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -915,14 +986,48 @@
       <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>COMP_018</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Verify @all mention</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify @all mention in group</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@all".
+2. Select from suggestions.
+3. Send.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Message should be sent; all members notified.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
@@ -930,7 +1035,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>COMP_010</t>
+          <t>COMP_020</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -940,29 +1045,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Verify Recording Button</t>
+          <t>Verify @ mention</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify voice recording and send</t>
+          <t>Verify @ shows member suggestions</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Press and hold mic button.
-2. Record.
-3. Release to send.</t>
+          <t>1. Type "@" in group chat.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Voice message should be sent with play button.</t>
+          <t>Member list with avatars should appear.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -977,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COMP_011</t>
+          <t>COMP_021</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -985,23 +1088,22 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify cancel recording</t>
+          <t>Verify filtering members by name</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Start recording.
-2. Slide to cancel.</t>
+          <t>1. Type "@Geo".</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Recording should be cancelled.</t>
+          <t>Only matching members should appear.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
       <c r="I16" s="2" t="n"/>
@@ -1011,29 +1113,26 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>COMP_012</t>
+          <t>COMP_022</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>User has received voice message</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify playing voice message</t>
+          <t>Verify sending @ mention message</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Click play on received voice message.</t>
+          <t>1. Select member.
+2. Send message.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Voice message should play with progress.</t>
+          <t>Mentioned user should receive notification.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1046,14 +1145,46 @@
       <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>COMP_024</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Verify Composer in One-on-One chat</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify all features work in direct chat</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Test send, attach, record, emoji, sticker.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>All features should work except @all.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
@@ -1061,38 +1192,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COMP_013</t>
+          <t>COMP_025</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Verify Recording Button</t>
+          <t>Verify Composer in Group chat</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, mic permission denied</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify recording without permission</t>
+          <t>Verify all features work in group chat</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Deny mic permission.
-2. Try to record.</t>
+          <t>1. Test all features including @mentions.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Permission request or error should display.</t>
+          <t>All features should work including @all and @.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1105,60 +1235,60 @@
       <c r="K19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>COMP_026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify composer on desktop and mobile</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Test on desktop.
+2. Test on mobile.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Composer should be functional on both platforms.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>COMP_014</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Verify Emoji Button</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify emoji picker opens and selection</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Click emoji button.
-2. Select emoji.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Emoji should be added to input field.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
@@ -1166,26 +1296,38 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COMP_015</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
+          <t>COMP_003</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send Button</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify sending message with emoji</t>
+          <t>Verify empty message not sent</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Add emoji to message.
-2. Send.</t>
+          <t>1. Leave input empty.
+2. Click send.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Message with emoji should display correctly.</t>
+          <t>Message should not be sent.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1200,37 +1342,30 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COMP_016</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Verify Sticker Button</t>
-        </is>
-      </c>
+          <t>COMP_004</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and chat is open</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify sticker picker opens</t>
+          <t>Verify send fails without network</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Click sticker button.</t>
+          <t>1. Disconnect network.
+2. Send message.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Sticker picker should open with sticker packs.</t>
+          <t>Error should display with retry option.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1245,31 +1380,42 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COMP_017</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
+          <t>COMP_008</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Verify Attach Button</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify sending sticker</t>
+          <t>Verify file size limit exceeded</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Open sticker picker.
-2. Click sticker.</t>
+          <t>1. Select file exceeding size limit.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Sticker should be sent and display in chat.</t>
+          <t>Error message should display.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -1279,39 +1425,30 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COMP_018</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all mention</t>
-        </is>
-      </c>
+          <t>COMP_009</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and group chat is open</t>
+          <t>User is logged in, network error</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify @all mention in group</t>
+          <t>Verify attachment upload failure</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Type "@all".
-2. Select from suggestions.
-3. Send.</t>
+          <t>1. Disconnect network.
+2. Send attachment.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Message should be sent; all members notified.</t>
+          <t>Error should display with retry option.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,14 +1461,47 @@
       <c r="K25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>COMP_013</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Recording Button</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, mic permission denied</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Verify recording without permission</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Deny mic permission.
+2. Try to record.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Permission request or error should display.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
@@ -1383,336 +1553,49 @@
       <c r="K27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>COMP_023</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ mention</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Verify @ with no matching members</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "@xyz123".</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No suggestions should appear.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>COMP_020</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ shows member suggestions</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@" in group chat.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Member list with avatars should appear.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>COMP_021</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Verify filtering members by name</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@Geo".</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Only matching members should appear.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>COMP_022</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending @ mention message</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Select member.
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Mentioned user should receive notification.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>COMP_023</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ with no matching members</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@xyz123".</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>No suggestions should appear.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>COMP_024</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Verify Composer in One-on-One chat</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Verify all features work in direct chat</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1. Test send, attach, record, emoji, sticker.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>All features should work except @all.</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>COMP_025</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Verify Composer in Group chat</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Verify all features work in group chat</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1. Test all features including @mentions.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>All features should work including @all and @.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>COMP_026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Verify composer on desktop and mobile</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Test on desktop.
-2. Test on mobile.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Composer should be functional on both platforms.</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2678,7 +2561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2795,64 +2678,89 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>COMP_045</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify attachment at exactly max file size</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Attach a file at exactly the maximum allowed size.
+2. Send.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>File should upload and send successfully.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>COMP_044</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message at max character limit + 1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to type one character beyond the max limit.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Input should be blocked or warning should display.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>COMP_044</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending message at max character limit + 1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to type one character beyond the max limit.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Input should be blocked or warning should display.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
@@ -2860,30 +2768,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>COMP_045</t>
+          <t>COMP_046</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify attachment at exactly max file size</t>
+          <t>Verify attachment at max file size + 1 byte</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Attach a file at exactly the maximum allowed size.
-2. Send.</t>
+          <t>1. Attach a file 1 byte over the maximum size.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>File should upload and send successfully.</t>
+          <t>Error message should display. File should not upload.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2894,56 +2801,6 @@
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>COMP_046</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment at max file size + 1 byte</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Attach a file 1 byte over the maximum size.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display. File should not upload.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Composer/Composer_Test_Cases.xlsx
+++ b/Composer/Composer_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,114 +465,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>COMP_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Send Button</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify send button sends text message</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type message.
 2. Click send button.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should be sent and appear in chat with timestamp.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -560,31 +570,31 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>COMP_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify Enter key sends message</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Type message.
 2. Press Enter key.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Message should be sent.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -594,42 +604,42 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>COMP_005</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Verify Attach Button</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify attach menu opens</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Click attach (+) button.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Attachment options should display (Image, Video, Document).</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -639,32 +649,32 @@
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>COMP_006</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify sending image attachment</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Click attach.
 2. Select image.
 3. Send.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Image should upload and display in chat.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -674,32 +684,32 @@
       <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>COMP_007</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify sending document attachment</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Click attach.
 2. Select document.
 3. Send.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Document should upload with file icon and name.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -709,44 +719,44 @@
       <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>COMP_010</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Verify Recording Button</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify voice recording and send</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Press and hold mic button.
 2. Record.
 3. Release to send.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Voice message should be sent with play button.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -756,31 +766,31 @@
       <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>COMP_011</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify cancel recording</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Start recording.
 2. Slide to cancel.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Recording should be cancelled.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
@@ -790,34 +800,34 @@
       <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>COMP_012</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>User has received voice message</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify playing voice message</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Click play on received voice message.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Voice message should play with progress.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -827,43 +837,43 @@
       <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>COMP_014</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Verify Emoji Button</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify emoji picker opens and selection</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Click emoji button.
 2. Select emoji.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Emoji should be added to input field.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -873,31 +883,31 @@
       <c r="K10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>COMP_015</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify sending message with emoji</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Add emoji to message.
 2. Send.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Message with emoji should display correctly.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -907,42 +917,42 @@
       <c r="K11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>COMP_016</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Verify Sticker Button</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify sticker picker opens</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Click sticker button.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -952,31 +962,31 @@
       <c r="K12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>COMP_017</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify sending sticker</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Open sticker picker.
 2. Click sticker.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Sticker should be sent and display in chat.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -986,44 +996,44 @@
       <c r="K13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>COMP_018</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Verify @all mention</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify @all mention in group</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Type "@all".
 2. Select from suggestions.
 3. Send.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Message should be sent; all members notified.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1033,42 +1043,42 @@
       <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>COMP_020</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Verify @ mention</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify @ shows member suggestions</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Type "@" in group chat.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Member list with avatars should appear.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1078,30 +1088,30 @@
       <c r="K15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>COMP_021</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify filtering members by name</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Type "@Geo".</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Only matching members should appear.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1111,31 +1121,31 @@
       <c r="K16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>COMP_022</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify sending @ mention message</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Select member.
 2. Send message.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Mentioned user should receive notification.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1145,42 +1155,42 @@
       <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>COMP_024</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Verify Composer in One-on-One chat</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify all features work in direct chat</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Test send, attach, record, emoji, sticker.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>All features should work except @all.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1190,42 +1200,42 @@
       <c r="K18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>COMP_025</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Verify Composer in Group chat</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify all features work in group chat</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Test all features including @mentions.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>All features should work including @all and @.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1235,43 +1245,43 @@
       <c r="K19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>COMP_026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify composer on desktop and mobile</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Test on desktop.
 2. Test on mobile.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Composer should be functional on both platforms.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
@@ -1281,56 +1291,73 @@
       <c r="K20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>COMP_004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Verify send fails without network</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Error should display with retry option.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>COMP_003</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send Button</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty message not sent</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1. Leave input empty.
-2. Click send.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Message should not be sent.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>COMP_009</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Verify attachment upload failure</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Send attachment.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Error should display with retry option.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1340,37 +1367,46 @@
       <c r="K22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>COMP_004</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify send fails without network</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Error should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>COMP_052</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Polls Creation</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>hidePollsOption=false, group chat</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Verify polls option visible in attachment menu</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1. Open group chat
+2. Click attachment button
+3. Check for polls</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Polls option visible in attachment actions</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I23" s="2" t="n"/>
@@ -1378,44 +1414,46 @@
       <c r="K23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>COMP_008</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Verify Attach Button</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Verify file size limit exceeded</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1. Select file exceeding size limit.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>COMP_053</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Polls Creation</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Polls option clicked</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Verify poll creation form opens</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1. Click polls option
+2. Fill question and options
+3. Submit</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Poll created and sent as interactive message</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
@@ -1423,37 +1461,45 @@
       <c r="K24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>COMP_009</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment upload failure</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Send attachment.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Error should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>COMP_054</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Collaborative Document</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>hideCollaborativeDocumentOption=false</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Verify collaborative document option in attachments</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Click collaborative document</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Collaborative document created and shared in chat</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25" s="2" t="n"/>
@@ -1461,45 +1507,45 @@
       <c r="K25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>COMP_013</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Verify Recording Button</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, mic permission denied</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Verify recording without permission</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1. Deny mic permission.
-2. Try to record.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Permission request or error should display.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>COMP_055</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Collaborative Whiteboard</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>hideCollaborativeWhiteboardOption=false</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Verify collaborative whiteboard option in attachments</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Click collaborative whiteboard</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Whiteboard session created and shared in chat</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I26" s="2" t="n"/>
@@ -1507,45 +1553,45 @@
       <c r="K26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>COMP_019</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all mention</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify @all not available in direct chat</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Open direct chat.
-2. Type "@all".</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>@all suggestion should not appear.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>COMP_056</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>AI Assistant Button</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>AI features enabled</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Verify AI assistant button appears in composer</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat with AI enabled
+2. Check composer buttons</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>AI assistant button visible in composer</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I27" s="2" t="n"/>
@@ -1553,49 +1599,1163 @@
       <c r="K27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>COMP_023</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ mention</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Verify @ with no matching members</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1. Type "@xyz123".</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No suggestions should appear.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>COMP_057</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>AI Assistant Interaction</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>AI button visible</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Verify AI assistant popover opens on click</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1. Click AI assistant button</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>AI assistant popover/panel opens with options</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>COMP_058</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Enter Key - Send Message</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>enterKeyBehavior=SendMessage (default)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Verify Enter key sends message</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1. Type message
+2. Press Enter</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Message sent immediately</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>COMP_059</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Enter Key - New Line</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>enterKeyBehavior=NewLine</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Verify Enter key adds new line</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1. Type message
+2. Press Enter</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>New line added to message, not sent</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>COMP_060</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Preview Mode - Edit</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>User clicks edit on a message</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Verify edit preview shown in composer</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1. Click edit on sent message
+2. Check composer header</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Edit preview banner shown with original message text</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>COMP_061</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Preview Mode - Reply</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>User clicks reply on a message</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Verify reply preview shown in composer</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1. Click reply on a message
+2. Check composer header</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Reply preview banner shown with referenced message</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>COMP_062</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Typing Events</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>disableTypingEvents=false (default)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing indicator sent when user types</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1. Start typing in composer
+2. Check other user's view</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Typing indicator shown to other participants</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>COMP_063</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Typing Events Stop</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>User stops typing</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing stopped event sent after 500ms</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1. Type then stop
+2. Wait 500ms</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Typing indicator removed for other users</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>COMP_064</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Mentions</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>disableMentions=false, group chat</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Verify @ mentions trigger user list</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '@' in composer
+2. Check for user list</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>User/member list appears for mention selection</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>COMP_065</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Mention All</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>disableMentionAll=false, group chat</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Verify @all mention option available</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '@'
+2. Check for 'all' option</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>@all option visible in mentions list</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>COMP_066</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Voice Recording</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>hideVoiceRecordingButton=false</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Verify voice recording button and functionality</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1. Click mic button
+2. Record audio
+3. Send</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Voice message recorded and sent</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>COMP_067</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Emoji Keyboard</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>hideEmojiKeyboardButton=false</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Verify emoji keyboard opens</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1. Click emoji button
+2. Select emoji</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Emoji inserted into message text</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>COMP_068</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Stickers</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>hideStickersButton=false</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Verify stickers button and panel</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1. Click stickers button
+2. Select sticker</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Sticker sent as message</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>COMP_003</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Verify Send Button</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty message not sent</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1. Leave input empty.
+2. Click send.</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Message should not be sent.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>COMP_008</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Verify Attach Button</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Verify file size limit exceeded</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1. Select file exceeding size limit.</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Error message should display.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>COMP_013</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Verify Recording Button</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, mic permission denied</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Verify recording without permission</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1. Deny mic permission.
+2. Try to record.</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Permission request or error should display.</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>COMP_019</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Verify @all mention</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Verify @all not available in direct chat</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>1. Open direct chat.
+2. Type "@all".</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>@all suggestion should not appear.</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>COMP_023</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Verify @ mention</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Verify @ with no matching members</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1. Type "@xyz123".</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>No suggestions should appear.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>COMP_069</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Polls Hidden</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>hidePollsOption=true</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Verify polls option hidden</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Check options</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Polls option not visible</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>COMP_070</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Collaborative Doc Hidden</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>hideCollaborativeDocumentOption=true</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Verify collaborative document hidden</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Check options</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Collaborative document option not visible</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>COMP_071</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Collaborative Whiteboard Hidden</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>hideCollaborativeWhiteboardOption=true</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Verify collaborative whiteboard hidden</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Check options</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Whiteboard option not visible</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>COMP_072</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Typing Events Disabled</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>disableTypingEvents=true</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Verify no typing indicator sent</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1. Type in composer
+2. Check other user</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>No typing indicator shown to others</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>COMP_073</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Mentions Disabled</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>disableMentions=true</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Verify @ does not trigger mentions</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '@' in composer</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>No user list appears</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>COMP_074</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Mention All Disabled</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>disableMentionAll=true</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Verify @all option not available</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '@'
+2. Check list</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>@all option not visible</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>COMP_075</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Voice Recording Hidden</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>hideVoiceRecordingButton=true</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Verify mic button hidden</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>1. Check composer buttons</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Voice recording button not visible</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>COMP_076</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Send Button Hidden</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>hideSendButton=true</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Verify send button hidden</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1. Type message
+2. Check for send button</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Send button not visible</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>COMP_077</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Attachment Button Hidden</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>hideAttachmentButton=true</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Verify attachment button hidden</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>1. Check composer buttons</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Attachment/plus button not visible</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>COMP_078</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Blocked User Composer</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>User blocked by recipient</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Verify composer disabled for blocked user</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1. Open chat with user who blocked you</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Composer disabled or shows blocked message</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1605,118 +2765,106 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>COMP_027</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Composer with Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify sent message appears in message list immediately</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type and send a message.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should appear at the bottom of message list instantly with 'sending' then 'sent' status.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1726,35 +2874,35 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>COMP_028</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Integration: Composer with Typing Indicator</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify typing in composer triggers typing indicator for receiver</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Start typing in composer.
 2. Check receiver's chat.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Receiver should see 'User is typing...' indicator.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -1764,35 +2912,35 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>COMP_029</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Integration: Composer with Reply</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify composer shows reply preview when replying</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Reply' on a message.
 2. Observe composer.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Reply preview should appear above input with original message snippet and close button.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1802,35 +2950,35 @@
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>COMP_030</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Integration: Composer with Edit</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify composer populates message text when editing</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Edit' on own message.
 2. Observe composer.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Composer should populate with the original message text, ready for editing.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1838,6 +2986,223 @@
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>COMP_079</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Poll + Group Members</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Group chat with members</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify poll visible to all group members</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Create poll in group
+2. Check other members</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>All members see the poll and can vote</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COMP_080</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Mentions + Message Send</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Mention selected</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify mentioned user receives notification</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Mention user with @
+2. Send message</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Mentioned user receives mention notification</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>COMP_081</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Edit Preview + Send</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Edit mode active</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify edited message updates in message list</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Edit message text
+2. Click send</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Message updated in list with 'edited' indicator</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>COMP_082</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Reply + Thread</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Reply to threaded message</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify reply links to correct message</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Reply to a message
+2. Send</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Reply shows reference to original message</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>COMP_083</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Voice Recording + Network Loss</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Recording in progress, network drops</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Verify recording handles network loss</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. Start recording
+2. Disconnect network
+3. Try to send</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Error shown, recording preserved or discarded gracefully</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1847,117 +3212,105 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>COMP_031</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Composer</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify composer clears after sending message</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type and send a message.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Composer input should clear completely after message is sent.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1967,32 +3320,32 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>COMP_032</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify composer state after switching conversations</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Type a draft in conversation A.
 2. Switch to conversation B.
 3. Switch back to A.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Draft text should either persist or clear based on app behavior. No cross-conversation text leaking.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -2002,32 +3355,32 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>COMP_033</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify composer after canceling reply/edit</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Start a reply.
 2. Cancel it.
 3. Type a new message.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Composer should return to normal state. New message should send as regular message, not reply.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -2035,6 +3388,183 @@
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>COMP_084</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Polls After App Restart</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Poll created previously</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify polls persist after app restart</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Create poll
+2. Restart app
+3. Check poll</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Poll still visible with votes intact</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>COMP_085</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Edit After Scroll</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>User scrolled up then edits</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify edit works after scrolling</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Scroll up
+2. Click edit on old message
+3. Edit and send</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Message edited successfully</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COMP_086</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Typing After Reconnect</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Network reconnected</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing events resume after reconnect</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect
+2. Reconnect
+3. Type</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Typing indicator works after reconnection</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>COMP_087</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Mentions After Member Leave</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Mentioned user left group</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify mention handling for departed member</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Mention user
+2. User leaves group
+3. Check message</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Mention still visible but user shown as unavailable</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2044,118 +3574,93 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>COMP_034</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Security: Composer</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify HTML/script injection via composer</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Type '&lt;script&gt;alert(document.cookie)&lt;/script&gt;' in composer.
-2. Send.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Message should be sent as plain text. No script execution on receiver's end.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>COMP_035</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Verify file upload validates file type</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to attach a .exe or .bat file via composer.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Dangerous file types should be blocked with appropriate error message.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
@@ -2165,30 +3670,30 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>COMP_035</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify file upload validates file type</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to attach a .exe or .bat file via composer.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Dangerous file types should be blocked with appropriate error message.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>COMP_036</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Verify attachment does not allow path traversal</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to upload a file with path traversal in filename (e.g., '../../etc/passwd').</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>File should be rejected or filename sanitized. No server-side path traversal.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
@@ -2198,37 +3703,180 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>COMP_036</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment does not allow path traversal</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to upload a file with path traversal in filename (e.g., '../../etc/passwd').</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>File should be rejected or filename sanitized. No server-side path traversal.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>COMP_088</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Poll XSS Prevention</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Malicious script in poll question</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify XSS sanitized in poll creation</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Create poll with &lt;script&gt; in question
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Script tags sanitized, poll displays safely</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>COMP_089</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Mention Injection</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Malicious mention format</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify mention format cannot inject code</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Craft malicious @mention
+2. Send</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Mention rendered safely without code execution</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COMP_034</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Security: Composer</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify HTML/script injection via composer</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '&lt;script&gt;alert(document.cookie)&lt;/script&gt;' in composer.
+2. Send.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Message should be sent as plain text. No script execution on receiver's end.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>COMP_090</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>File Upload Malware</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Malicious file attachment</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify file validation on upload</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to upload executable file
+2. Check validation</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Dangerous file types rejected or warned</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2242,114 +3890,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>COMP_037</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Composer</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify composer with rapid send button clicks</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type a message.
 2. Click send button 10 times rapidly.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should be sent only once. No duplicate messages.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -2359,31 +3995,31 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>COMP_038</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify paste large text from clipboard</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Copy 50000 characters.
 2. Paste into composer.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Text should paste (may be truncated at limit). No crash or freeze.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2393,30 +4029,30 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>COMP_039</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify composer with multiple attachments simultaneously</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Select 5+ files at once for attachment.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>All files should queue for upload or show max attachment limit message.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2426,31 +4062,31 @@
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>COMP_040</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify emoji picker with search</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
 2. Search for 'smile'.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Matching emojis should filter and display. Selecting one should insert into composer.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2460,31 +4096,31 @@
       <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>COMP_041</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify sticker picker categories</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Open sticker picker.
 2. Browse categories.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Sticker categories should load. Selecting a sticker should send it.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2494,60 +4130,222 @@
       <c r="K6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COMP_091</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Poll with Max Options</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Poll with many options</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify poll handles maximum options</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Create poll with 10+ options</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Poll created with all options visible</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>COMP_092</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Rapid Typing Events</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>User types very fast</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify typing events don't flood</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Type rapidly for 5 seconds</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Typing events throttled appropriately</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>COMP_093</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Mention in Long Message</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Message with 5000+ chars and mentions</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify mentions work in long messages</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Type long message with @mentions
+2. Send</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Mentions highlighted correctly in long message</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>COMP_042</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Composer</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify composer when keyboard is dismissed mid-typing</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Start typing.
 2. Dismiss keyboard (mobile).
 3. Reopen keyboard.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Typed text should persist. No data loss.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>COMP_094</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empty Poll Submit</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>No question entered</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty poll cannot be submitted</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. Open poll creation
+2. Leave question empty
+3. Try submit</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Validation error shown</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2561,114 +4359,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>COMP_043</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Composer</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify sending message at exactly max character limit</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type exactly the maximum allowed characters.
 2. Send.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should send successfully.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2678,35 +4464,35 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>COMP_045</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify attachment at exactly max file size</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Attach a file at exactly the maximum allowed size.
 2. Send.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>File should upload and send successfully.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2716,49 +4502,90 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>COMP_095</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Poll Question Min Length</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1 character question</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify minimum poll question length</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter 1 char question
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Poll created with 1 char question</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>COMP_044</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending message at max character limit + 1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to type one character beyond the max limit.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Input should be blocked or warning should display.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>COMP_096</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Mention Search Min</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1 character after @</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify mention search with 1 char</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '@a'</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Users starting with 'a' shown</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" s="2" t="n"/>
@@ -2766,41 +4593,128 @@
       <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>COMP_046</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify attachment at max file size + 1 byte</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Attach a file 1 byte over the maximum size.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display. File should not upload.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COMP_044</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify sending message at max character limit + 1</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to type one character beyond the max limit.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Input should be blocked or warning should display.</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>COMP_046</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify attachment at max file size + 1 byte</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Attach a file 1 byte over the maximum size.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Error message should display. File should not upload.</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>COMP_097</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Poll Question Max Length</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Very long question (1000+ chars)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify poll question length limit</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter 1000+ char question
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate length limit enforced or handled</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2814,114 +4728,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual Result </t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Input Data</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>COMP_047</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Input Types</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify sending plain text message</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type plain English text.
 2. Send.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Message should send and display correctly.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -2931,31 +4833,31 @@
       <c r="K2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>COMP_048</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify sending message with only emojis</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Select emojis only from picker.
 2. Send.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Emoji message should send and display in larger size.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2965,31 +4867,31 @@
       <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>COMP_049</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify sending message with mixed text and emojis</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Type text with emojis interspersed.
 2. Send.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Message should display with inline emojis at normal text size.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2999,31 +4901,31 @@
       <c r="K4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>COMP_050</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify sending message with only numbers</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Type '1234567890'.
 2. Send.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Numeric message should send and display correctly. Should not be interpreted as phone number unless intended.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
@@ -3033,31 +4935,31 @@
       <c r="K5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>COMP_051</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify sending message with URLs</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Type a message containing 'https://example.com'.
 2. Send.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>URL should be clickable/tappable in the sent message. Link preview may generate.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -3065,6 +4967,225 @@
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>COMP_098</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Attachment - Image</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Image file selected</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify image attachment upload</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Select image
+3. Send</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Image uploaded and displayed in chat</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>COMP_099</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Attachment - Video</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Video file selected</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify video attachment upload</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Select video
+3. Send</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Video uploaded and playable in chat</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>COMP_100</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Attachment - Audio</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Audio file selected</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio attachment upload</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Select audio
+3. Send</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Audio uploaded and playable in chat</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>COMP_101</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Attachment - File</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Document file selected</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify file attachment upload</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Click attachment
+2. Select document
+3. Send</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>File uploaded with download option</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>COMP_102</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Attachment - Invalid Type</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Unsupported file type</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Verify invalid file type rejected</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to upload unsupported file</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>File rejected with appropriate error</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
